--- a/results/qwen3_5_9b/comparison_SimpleRAG/SimpleRAG_evaluated.xlsx
+++ b/results/qwen3_5_9b/comparison_SimpleRAG/SimpleRAG_evaluated.xlsx
@@ -505,35 +505,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01010100960871342</v>
+        <v>0.179999995410889</v>
       </c>
       <c r="D2" t="n">
-        <v>7.188271943170174e-260</v>
+        <v>0.02185874490760725</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3537169694900513</v>
+        <v>0.6043150424957275</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.694999999999993</v>
+        <v>23.48171289241085</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07379375591296121</v>
+        <v>0.651844843897824</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2622950819672131</v>
       </c>
     </row>
     <row r="3">
@@ -546,19 +548,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.1599999968000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3.162429961676339e-155</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4298741221427917</v>
+        <v>0.5548350214958191</v>
       </c>
       <c r="F3" t="n">
-        <v>-6.694999999999993</v>
+        <v>16.766847826087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7155963302752294</v>
+        <v>2.339449541284404</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -566,15 +568,17 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1208791208791209</v>
       </c>
     </row>
     <row r="4">
@@ -587,35 +591,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.2396313323638217</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.003751756555926853</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2991204261779785</v>
+        <v>0.6371692419052124</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.694999999999993</v>
+        <v>31.87099483204136</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.405982905982906</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="n">
         <v>0.5</v>
       </c>
       <c r="L4" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.25</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="5">
@@ -628,35 +634,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.2413793065776457</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.077201656108163e-79</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2943938076496124</v>
+        <v>0.6558974385261536</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.694999999999993</v>
+        <v>52.62126859504136</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06382978723404255</v>
+        <v>0.3649754500818331</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.4406779661016949</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2682926829268293</v>
       </c>
     </row>
     <row r="6">
@@ -669,35 +677,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.17592592175583</v>
       </c>
       <c r="D6" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>5.513513681957571e-156</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3298570215702057</v>
+        <v>0.6085430383682251</v>
       </c>
       <c r="F6" t="n">
-        <v>-6.694999999999993</v>
+        <v>45.97646464646465</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0896551724137931</v>
+        <v>0.4367816091954023</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2134831460674157</v>
       </c>
     </row>
     <row r="7">
@@ -710,19 +720,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004032257864935623</v>
+        <v>0.08598130690163334</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3.813999754289355e-88</v>
       </c>
       <c r="E7" t="n">
-        <v>0.353213906288147</v>
+        <v>0.550951361656189</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.694999999999993</v>
+        <v>15.92500000000004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02269421006691882</v>
+        <v>0.08961303462321792</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -730,15 +740,17 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" t="n">
         <v>0.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.25</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.2063492063492064</v>
       </c>
     </row>
     <row r="8">
@@ -751,35 +763,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.1880877702168808</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3.782611663077085e-79</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3415371477603912</v>
+        <v>0.5955166816711426</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.694999999999993</v>
+        <v>33.44761904761904</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05416666666666667</v>
+        <v>0.425</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
         <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4214876033057851</v>
       </c>
     </row>
     <row r="9">
@@ -792,35 +806,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006993006649469429</v>
+        <v>0.1520467806947437</v>
       </c>
       <c r="D9" t="n">
-        <v>4.626996437597695e-283</v>
+        <v>4.184799915876941e-158</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3237474858760834</v>
+        <v>0.6195626854896545</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.694999999999993</v>
+        <v>33.65204113924054</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04519119351100811</v>
+        <v>0.2195828505214369</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.25</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1954022988505747</v>
       </c>
     </row>
     <row r="10">
@@ -833,35 +849,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.1733333300935556</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1.587341920964993e-79</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3335631489753723</v>
+        <v>0.5963821411132812</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.19006787330318</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05158730158730158</v>
+        <v>0.3108465608465609</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="11">
@@ -874,19 +892,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006756756424625656</v>
+        <v>0.124629077761361</v>
       </c>
       <c r="D11" t="n">
-        <v>3.199290466293744e-295</v>
+        <v>2.727136953450956e-157</v>
       </c>
       <c r="E11" t="n">
-        <v>0.312595933675766</v>
+        <v>0.5827984213829041</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.694999999999993</v>
+        <v>64.90326271186441</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04264625478403499</v>
+        <v>0.1864406779661017</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -894,15 +912,17 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.25</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3150684931506849</v>
       </c>
     </row>
     <row r="12">
@@ -915,19 +935,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1049382693028883</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1.048187222786645e-159</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3295387625694275</v>
+        <v>0.5294414758682251</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.694999999999993</v>
+        <v>28.63250000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04441913439635535</v>
+        <v>0.1588838268792711</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -935,15 +955,17 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.25</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="13">
@@ -956,35 +978,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006644517945718055</v>
+        <v>0.2347188224068484</v>
       </c>
       <c r="D13" t="n">
-        <v>1.737745674680046e-291</v>
+        <v>2.975131617077811e-156</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3309608399868011</v>
+        <v>0.6754701137542725</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.694999999999993</v>
+        <v>66.7609429280397</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04323725055432372</v>
+        <v>0.3519955654101996</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.25</v>
+        <v>0.303370786516854</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3137254901960784</v>
       </c>
     </row>
     <row r="14">
@@ -997,35 +1021,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.2222222190895062</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.002357693107793789</v>
       </c>
       <c r="E14" t="n">
-        <v>0.327696293592453</v>
+        <v>0.6467728018760681</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.694999999999993</v>
+        <v>60.64184210526318</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04333333333333333</v>
+        <v>0.2838888888888889</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L14" t="n">
-        <v>0.25</v>
+        <v>0.2586206896551724</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3167701863354037</v>
       </c>
     </row>
     <row r="15">
@@ -1038,35 +1064,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2620689612366231</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2.209311391872408e-155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3345783352851868</v>
+        <v>0.5793872475624084</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.694999999999993</v>
+        <v>71.79366847826088</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1569416498993964</v>
+        <v>0.6016096579476862</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.25</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2052980132450331</v>
       </c>
     </row>
     <row r="16">
@@ -1079,35 +1107,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2090909042400828</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>7.595063987954255e-79</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3279084861278534</v>
+        <v>0.6596572995185852</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.694999999999993</v>
+        <v>43.52261871013468</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1112696148359486</v>
+        <v>0.8316690442225392</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2405063291139241</v>
       </c>
     </row>
     <row r="17">
@@ -1120,35 +1150,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.2629107934801296</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1.169723085527137e-78</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3277542293071747</v>
+        <v>0.6602102518081665</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.694999999999993</v>
+        <v>52.49178571428573</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1048387096774194</v>
+        <v>0.6559139784946236</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0.3859649122807017</v>
+      </c>
+      <c r="M17" t="n">
         <v>0.25</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="18">
@@ -1161,35 +1193,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.2127659538821276</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.01009982552860134</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3615763187408447</v>
+        <v>0.6351878046989441</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.694999999999993</v>
+        <v>61.82779596376926</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03037383177570093</v>
+        <v>0.2866043613707165</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.25</v>
+        <v>0.3061224489795918</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3181818181818182</v>
       </c>
     </row>
     <row r="19">
@@ -1202,19 +1236,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1774743999906813</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1.023503195059246e-81</v>
       </c>
       <c r="E19" t="n">
-        <v>0.33333620429039</v>
+        <v>0.5886138081550598</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.694999999999993</v>
+        <v>33.78275000000002</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05141727092946605</v>
+        <v>0.2050098879367172</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1222,15 +1256,17 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.25</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.140625</v>
       </c>
     </row>
     <row r="20">
@@ -1243,35 +1279,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008032128120514206</v>
+        <v>0.1973333287873423</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21304235279905e-268</v>
+        <v>6.643163136378773e-79</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3513511121273041</v>
+        <v>0.6310942769050598</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.72181343283583</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05535841022001419</v>
+        <v>0.609652235628105</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.25</v>
+        <v>0.2551020408163265</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.3805309734513274</v>
       </c>
     </row>
     <row r="21">
@@ -1284,35 +1322,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.2379603360094376</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.005594593414339694</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3501014113426208</v>
+        <v>0.573747992515564</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.694999999999993</v>
+        <v>55.36715172413795</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04419263456090652</v>
+        <v>0.3473087818696884</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>0.25</v>
+        <v>0.2716049382716049</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.08653846153846154</v>
       </c>
     </row>
     <row r="22">
@@ -1325,19 +1365,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.1319444424153646</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>7.035603749466021e-84</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3600354492664337</v>
+        <v>0.5146150588989258</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.694999999999993</v>
+        <v>40.17500000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04727272727272727</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1345,15 +1385,17 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.25</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="23">
@@ -1366,35 +1408,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005847952928251443</v>
+        <v>0.313167254985056</v>
       </c>
       <c r="D23" t="n">
-        <v>1.811128572821972e-307</v>
+        <v>1.159770719131815e-78</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3535859286785126</v>
+        <v>0.6761953830718994</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.694999999999993</v>
+        <v>29.33769841269844</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0358291226458429</v>
+        <v>0.7005052824988516</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
         <v>0.5</v>
       </c>
       <c r="L23" t="n">
-        <v>0.25</v>
+        <v>0.182741116751269</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.7313432835820896</v>
       </c>
     </row>
     <row r="24">
@@ -1407,35 +1451,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.2545454498850322</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1.84425286803067e-155</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3177126049995422</v>
+        <v>0.6434938311576843</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.694999999999993</v>
+        <v>15.46001612903228</v>
       </c>
       <c r="G24" t="n">
-        <v>0.119815668202765</v>
+        <v>0.663594470046083</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.25</v>
+        <v>0.3061224489795918</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2024539877300613</v>
       </c>
     </row>
     <row r="25">
@@ -1448,35 +1494,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2386363590399019</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5.87773382411675e-79</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3314136564731598</v>
+        <v>0.6541544795036316</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.694999999999993</v>
+        <v>47.69637254901963</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.5987933634992458</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="M25" t="n">
         <v>0.25</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="26">
@@ -1489,35 +1537,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.2624999951757813</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>9.346427289419537e-79</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3261704742908478</v>
+        <v>0.6397182941436768</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.694999999999993</v>
+        <v>22.86719230769236</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1351819757365685</v>
+        <v>0.7435008665511266</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
         <v>0.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.25</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2771084337349398</v>
       </c>
     </row>
     <row r="27">
@@ -1530,35 +1580,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.2553191445523993</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>3.970998524709027e-79</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3252985775470734</v>
+        <v>0.6008229851722717</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.694999999999993</v>
+        <v>35.57723837209303</v>
       </c>
       <c r="G27" t="n">
-        <v>0.106703146374829</v>
+        <v>0.53077975376197</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2405063291139241</v>
       </c>
     </row>
     <row r="28">
@@ -1571,35 +1623,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.2699386460536716</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3.206501399135887e-79</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3308320045471191</v>
+        <v>0.5576639771461487</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.92565217391305</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1181818181818182</v>
+        <v>0.4575757575757576</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.25</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1891891891891892</v>
       </c>
     </row>
     <row r="29">
@@ -1612,35 +1666,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.2598870006766894</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1.171572819558805e-78</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3268276154994965</v>
+        <v>0.6349772810935974</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.694999999999993</v>
+        <v>14.28452702702705</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1354166666666667</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
         <v>0.5</v>
       </c>
       <c r="L29" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.358974358974359</v>
       </c>
     </row>
     <row r="30">
@@ -1653,35 +1709,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.1052631558067867</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1.731819436118073e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4468841254711151</v>
+        <v>0.5131526589393616</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.694999999999993</v>
+        <v>59.263688172043</v>
       </c>
       <c r="G30" t="n">
-        <v>0.78</v>
+        <v>4.76</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.25</v>
+        <v>0.3148148148148148</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2352941176470588</v>
       </c>
     </row>
     <row r="31">
@@ -1694,35 +1752,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1282051261637081</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1.97145351198676e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4375941157341003</v>
+        <v>0.5361713171005249</v>
       </c>
       <c r="F31" t="n">
-        <v>-6.694999999999993</v>
+        <v>65.55811904761907</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7572815533980582</v>
+        <v>4.456310679611651</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="32">
@@ -1735,35 +1795,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.1204819257773262</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1.867555914367928e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4345121085643768</v>
+        <v>0.5348336100578308</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.694999999999993</v>
+        <v>48.09089285714288</v>
       </c>
       <c r="G32" t="n">
-        <v>0.78</v>
+        <v>4.78</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2265193370165746</v>
       </c>
     </row>
     <row r="33">
@@ -1776,35 +1838,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.2205882305374136</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>0.02509047081322424</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4005701541900635</v>
+        <v>0.6044853925704956</v>
       </c>
       <c r="F33" t="n">
-        <v>-6.694999999999993</v>
+        <v>61.90204678362574</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2160664819944598</v>
+        <v>1.556786703601108</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>0.25</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.281437125748503</v>
       </c>
     </row>
     <row r="34">
@@ -1817,35 +1881,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.1808510591557267</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>2.075505785857712e-155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3832495212554932</v>
+        <v>0.5973866581916809</v>
       </c>
       <c r="F34" t="n">
-        <v>-6.694999999999993</v>
+        <v>66.15478571428574</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1133720930232558</v>
+        <v>0.6540697674418605</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
-        <v>0.25</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2631578947368421</v>
       </c>
     </row>
     <row r="35">
@@ -1858,35 +1924,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.3696969649092746</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.06019347783543957</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3523319959640503</v>
+        <v>0.6811069846153259</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.694999999999993</v>
+        <v>45.93392717086837</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06830122591943957</v>
+        <v>0.6611208406304728</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.25</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="M35" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4262295081967214</v>
       </c>
     </row>
     <row r="36">
@@ -1899,35 +1967,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2424242376283033</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1.190965541157402e-78</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3204767107963562</v>
+        <v>0.6990688443183899</v>
       </c>
       <c r="F36" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.22437500000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1236133122028526</v>
+        <v>0.8145800316957211</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.25</v>
+        <v>0.3220338983050847</v>
       </c>
       <c r="M36" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3061224489795918</v>
       </c>
     </row>
     <row r="37">
@@ -1940,35 +2010,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.1089108875718068</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>3.996388526558475e-156</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3582548201084137</v>
+        <v>0.5503356456756592</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.694999999999993</v>
+        <v>28.04540140845072</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08271474019088017</v>
+        <v>0.3435843054082715</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.25</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2553191489361702</v>
       </c>
     </row>
     <row r="38">
@@ -1981,35 +2053,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2068965470649617</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2.179480756627313e-155</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3565259277820587</v>
+        <v>0.5841172337532043</v>
       </c>
       <c r="F38" t="n">
-        <v>-6.694999999999993</v>
+        <v>36.20016806722691</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1009055627425614</v>
+        <v>0.6015523932729625</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
-        <v>0.5</v>
+        <v>0.925</v>
       </c>
       <c r="L38" t="n">
-        <v>0.25</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3658536585365854</v>
       </c>
     </row>
     <row r="39">
@@ -2022,35 +2096,37 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2587064627063687</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.02459307181097702</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3533079922199249</v>
+        <v>0.6409978270530701</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.694999999999993</v>
+        <v>41.64287439613528</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1150442477876106</v>
+        <v>0.855457227138643</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.25</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2424242424242424</v>
       </c>
     </row>
     <row r="40">
@@ -2063,35 +2139,37 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.3399209438528957</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.0315443883087062</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2973054349422455</v>
+        <v>0.6457474827766418</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.694999999999993</v>
+        <v>49.31608241758244</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08590308370044053</v>
+        <v>0.6806167400881057</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.25</v>
+        <v>0.325</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3548387096774193</v>
       </c>
     </row>
     <row r="41">
@@ -2104,35 +2182,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2462462426271316</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.003115038339575822</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2983242273330688</v>
+        <v>0.5215330123901367</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.694999999999993</v>
+        <v>59.70530000000002</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05349794238683128</v>
+        <v>0.3244170096021948</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0.25</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="42">
@@ -2145,35 +2225,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.215246632430976</v>
       </c>
       <c r="D42" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>2.337053317910161e-79</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3304620385169983</v>
+        <v>0.6265702843666077</v>
       </c>
       <c r="F42" t="n">
-        <v>-6.694999999999993</v>
+        <v>55.59536512027492</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08914285714285715</v>
+        <v>0.4788571428571429</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
         <v>0.5</v>
       </c>
       <c r="L42" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="M42" t="n">
         <v>0.25</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="43">
@@ -2186,35 +2268,37 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2238805923758076</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.02769771884910523</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3637755811214447</v>
+        <v>0.6200291514396667</v>
       </c>
       <c r="F43" t="n">
-        <v>-6.694999999999993</v>
+        <v>24.72375</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07228915662650602</v>
+        <v>0.556997219647822</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.25</v>
+        <v>0.2875</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.1372549019607843</v>
       </c>
     </row>
     <row r="44">
@@ -2227,19 +2311,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.1916666623697918</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.02872767822183733</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3320682942867279</v>
+        <v>0.6812066435813904</v>
       </c>
       <c r="F44" t="n">
-        <v>-6.694999999999993</v>
+        <v>32.76696078431374</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08955223880597014</v>
+        <v>0.5040183696900115</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2247,15 +2331,17 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
       <c r="K44" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0.25</v>
+        <v>0.3275862068965517</v>
       </c>
       <c r="M44" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="45">
@@ -2268,35 +2354,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1232394348990776</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1.012019744289022e-162</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3620854616165161</v>
+        <v>0.5612558722496033</v>
       </c>
       <c r="F45" t="n">
-        <v>-6.694999999999993</v>
+        <v>19.33928767123288</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02138744173293118</v>
+        <v>0.08774335069920483</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L45" t="n">
-        <v>0.25</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="M45" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1397849462365592</v>
       </c>
     </row>
     <row r="46">
@@ -2309,35 +2397,37 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1900452459622039</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.0008419932130876846</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3481395244598389</v>
+        <v>0.6237825155258179</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.694999999999993</v>
+        <v>55.09198679471791</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02160066463583495</v>
+        <v>0.198283024093049</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="L46" t="n">
-        <v>0.25</v>
+        <v>0.2929292929292929</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3805309734513274</v>
       </c>
     </row>
     <row r="47">
@@ -2350,35 +2440,37 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2260869536201323</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>9.627878809907659e-81</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3639097213745117</v>
+        <v>0.6099787950515747</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.694999999999993</v>
+        <v>39.87156125608141</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0310880829015544</v>
+        <v>0.2088481466719809</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L47" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M47" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2473118279569892</v>
       </c>
     </row>
     <row r="48">
@@ -2391,35 +2483,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2061855636178128</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.01269830595365195</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3680242300033569</v>
+        <v>0.609144389629364</v>
       </c>
       <c r="F48" t="n">
-        <v>-6.694999999999993</v>
+        <v>35.70947058823532</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1670235546038544</v>
+        <v>0.4047109207708779</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0.25</v>
+        <v>0.3125</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="49">
@@ -2432,35 +2526,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1925925880537724</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>6.441354551294798e-79</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3522202372550964</v>
+        <v>0.6491268873214722</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.694999999999993</v>
+        <v>42.95500000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1502890173410405</v>
+        <v>0.6782273603082851</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.25</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.178743961352657</v>
       </c>
     </row>
     <row r="50">
@@ -2473,35 +2569,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.3195266222275131</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1.573355140088374e-78</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3514077365398407</v>
+        <v>0.6513027548789978</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.694999999999993</v>
+        <v>45.32678160919542</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1494252873563219</v>
+        <v>0.9885057471264368</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L50" t="n">
-        <v>0.25</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="M50" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2528735632183908</v>
       </c>
     </row>
     <row r="51">
@@ -2514,35 +2612,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.3278688474593524</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.03185554685144382</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3513664901256561</v>
+        <v>0.6248700022697449</v>
       </c>
       <c r="F51" t="n">
-        <v>-6.694999999999993</v>
+        <v>39.15545517241384</v>
       </c>
       <c r="G51" t="n">
-        <v>0.103861517976032</v>
+        <v>1.049267643142477</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L51" t="n">
-        <v>0.25</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="M51" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3809523809523809</v>
       </c>
     </row>
     <row r="52">
@@ -2555,35 +2655,37 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008403360933196829</v>
+        <v>0.1868512079481807</v>
       </c>
       <c r="D52" t="n">
-        <v>2.960553565183628e-265</v>
+        <v>4.84516557083318e-157</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3619620203971863</v>
+        <v>0.5342695713043213</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.694999999999993</v>
+        <v>33.09357142857144</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05656272661348803</v>
+        <v>0.2487309644670051</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.25</v>
+        <v>0.2040816326530612</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1566265060240964</v>
       </c>
     </row>
     <row r="53">
@@ -2596,35 +2698,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.3801295849631243</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.05221164602881641</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3393140435218811</v>
+        <v>0.669135570526123</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.694999999999993</v>
+        <v>46.60702172067357</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0416221985058698</v>
+        <v>0.6558164354322306</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0.25</v>
+        <v>0.3356164383561644</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.5283018867924528</v>
       </c>
     </row>
     <row r="54">
@@ -2637,35 +2741,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.1610738212873295</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>6.357767916732833e-80</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3256970345973969</v>
+        <v>0.6112699508666992</v>
       </c>
       <c r="F54" t="n">
-        <v>-6.694999999999993</v>
+        <v>-5.659957264957228</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05739514348785872</v>
+        <v>0.4392935982339956</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L54" t="n">
-        <v>0.25</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="55">
@@ -2678,35 +2784,37 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.1678832092373062</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>6.524324042578614e-06</v>
       </c>
       <c r="E55" t="n">
-        <v>0.343548446893692</v>
+        <v>0.5519033670425415</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.694999999999993</v>
+        <v>37.45538461538465</v>
       </c>
       <c r="G55" t="n">
-        <v>0.05045278137128072</v>
+        <v>0.165588615782665</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
         <v>0.5</v>
       </c>
       <c r="L55" t="n">
-        <v>0.25</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1463414634146341</v>
       </c>
     </row>
     <row r="56">
@@ -2725,13 +2833,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3342143893241882</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.694999999999993</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.04977664326738992</v>
+        <v>0.02616464582003829</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2741,10 +2849,10 @@
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L56" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0.1111111111111111</v>
@@ -2760,35 +2868,37 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.2461059148106094</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2.471901070465728e-79</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3695140182971954</v>
+        <v>0.6101638078689575</v>
       </c>
       <c r="F57" t="n">
-        <v>-6.694999999999993</v>
+        <v>24.90221861471866</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02687801516195727</v>
+        <v>0.4390075809786354</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
       <c r="K57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.25</v>
+        <v>0.225</v>
       </c>
       <c r="M57" t="n">
-        <v>0.04</v>
+        <v>0.3827160493827161</v>
       </c>
     </row>
     <row r="58">
@@ -2801,35 +2911,37 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.0120481921868196</v>
+        <v>0.2452830138687157</v>
       </c>
       <c r="D58" t="n">
-        <v>3.542014107114671e-257</v>
+        <v>3.707332481493019e-155</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3487640619277954</v>
+        <v>0.6791971325874329</v>
       </c>
       <c r="F58" t="n">
-        <v>-6.694999999999993</v>
+        <v>28.27533766233768</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08423326133909287</v>
+        <v>1.120950323974082</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>0.25</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.393939393939394</v>
       </c>
     </row>
     <row r="59">
@@ -2842,35 +2954,37 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.2135922283042701</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>2.022400060987183e-155</v>
       </c>
       <c r="E59" t="n">
-        <v>0.359289288520813</v>
+        <v>0.5963390469551086</v>
       </c>
       <c r="F59" t="n">
-        <v>-6.694999999999993</v>
+        <v>52.82705128205131</v>
       </c>
       <c r="G59" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.6351010101010101</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.25</v>
+        <v>0.2054794520547945</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4117647058823529</v>
       </c>
     </row>
     <row r="60">
@@ -2883,35 +2997,37 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.00446428549356267</v>
+        <v>0.203147348719794</v>
       </c>
       <c r="D60" t="n">
-        <v>8.265132997605698e-314</v>
+        <v>0.01220172814257362</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3573783934116364</v>
+        <v>0.6206266283988953</v>
       </c>
       <c r="F60" t="n">
-        <v>-6.694999999999993</v>
+        <v>14.97697631980989</v>
       </c>
       <c r="G60" t="n">
-        <v>0.02725366876310273</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.25</v>
+        <v>0.1878172588832487</v>
       </c>
       <c r="M60" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4774346793349169</v>
       </c>
     </row>
     <row r="61">
@@ -2924,35 +3040,37 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.1759999964364801</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>2.208023144735344e-155</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3793801069259644</v>
+        <v>0.4606733024120331</v>
       </c>
       <c r="F61" t="n">
-        <v>-6.694999999999993</v>
+        <v>54.98732605042017</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3157894736842105</v>
+        <v>2.595141700404858</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.25</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.3248945147679325</v>
       </c>
     </row>
     <row r="62">
@@ -2965,35 +3083,37 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.2480620105907098</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.03041493233714596</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3254241049289703</v>
+        <v>0.61978679895401</v>
       </c>
       <c r="F62" t="n">
-        <v>-6.694999999999993</v>
+        <v>31.99792910447763</v>
       </c>
       <c r="G62" t="n">
-        <v>0.195</v>
+        <v>0.8475</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.25</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="M62" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1304347826086956</v>
       </c>
     </row>
     <row r="63">
@@ -3006,35 +3126,37 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.234234229430647</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>2.194555027898429e-155</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3176030814647675</v>
+        <v>0.6234097480773926</v>
       </c>
       <c r="F63" t="n">
-        <v>-6.694999999999993</v>
+        <v>36.95215909090911</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1087866108786611</v>
+        <v>0.7629009762900977</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L63" t="n">
-        <v>0.25</v>
+        <v>0.352112676056338</v>
       </c>
       <c r="M63" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2248062015503876</v>
       </c>
     </row>
     <row r="64">
@@ -3047,35 +3169,37 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.226804118801148</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>3.230620562952813e-155</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3184672594070435</v>
+        <v>0.6041204333305359</v>
       </c>
       <c r="F64" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.92322139303485</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1278688524590164</v>
+        <v>0.8557377049180328</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.25</v>
+        <v>0.3013698630136986</v>
       </c>
       <c r="M64" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2307692307692307</v>
       </c>
     </row>
     <row r="65">
@@ -3088,35 +3212,37 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.2624999951531251</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>2.932777909177495e-155</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3219119608402252</v>
+        <v>0.6280467510223389</v>
       </c>
       <c r="F65" t="n">
-        <v>-6.694999999999993</v>
+        <v>50.32833333333338</v>
       </c>
       <c r="G65" t="n">
-        <v>0.156312625250501</v>
+        <v>0.7615230460921844</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L65" t="n">
-        <v>0.25</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="M65" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="66">
@@ -3129,35 +3255,37 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.2198952844691758</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1.400153425506653e-79</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3294911682605743</v>
+        <v>0.6040650010108948</v>
       </c>
       <c r="F66" t="n">
-        <v>-6.694999999999993</v>
+        <v>66.61068548387098</v>
       </c>
       <c r="G66" t="n">
-        <v>0.09786700125470514</v>
+        <v>0.3801756587202008</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.25</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="M66" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1891891891891892</v>
       </c>
     </row>
     <row r="67">
@@ -3170,35 +3298,37 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.2542372831715025</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>9.709914888250491e-79</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3287849128246307</v>
+        <v>0.6543359160423279</v>
       </c>
       <c r="F67" t="n">
-        <v>-6.694999999999993</v>
+        <v>46.10734265734266</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1068493150684932</v>
+        <v>0.9027397260273973</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
       <c r="K67" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.25</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="M67" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2741935483870968</v>
       </c>
     </row>
     <row r="68">
@@ -3211,35 +3341,37 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.09523809377676999</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1.502992793091532e-155</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4152870178222656</v>
+        <v>0.4814099669456482</v>
       </c>
       <c r="F68" t="n">
-        <v>-6.694999999999993</v>
+        <v>37.07089673913046</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6141732283464567</v>
+        <v>9.700787401574804</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L68" t="n">
-        <v>0.25</v>
+        <v>0.2467532467532468</v>
       </c>
       <c r="M68" t="n">
-        <v>0.2</v>
+        <v>0.6685082872928176</v>
       </c>
     </row>
   </sheetData>
